--- a/.cursor/_olds/info/product_routing_rules.xlsx
+++ b/.cursor/_olds/info/product_routing_rules.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\_PROJECTS\MES_midex\.cursor\_olds\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ADDB33-C65F-4BF0-BEF4-13210CFA7760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2861E3C8-C06F-4C04-965D-2CE964678D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="21429" xr2:uid="{383DB60B-F56E-4E1D-97DA-0913C612F016}"/>
   </bookViews>
   <sheets>
     <sheet name="product_routing_rules" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -69,9 +69,6 @@
     <t xml:space="preserve"> GECO Крем_гель для очистки рук тела и волос, 2 л, Картридж, Крышка </t>
   </si>
   <si>
-    <t xml:space="preserve"> 00-000931 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> GECO Крем гидрофильный СП, 100 мл, Лам, Винт </t>
   </si>
   <si>
@@ -340,6 +337,9 @@
   </si>
   <si>
     <t>WC_SEMI_AUTO_LIQUID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 00-000968 </t>
   </si>
 </sst>
 </file>
@@ -746,7 +746,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -768,13 +768,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -782,13 +782,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -796,13 +796,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -810,13 +810,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -824,13 +824,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -838,13 +838,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -852,13 +852,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -866,13 +866,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -880,13 +880,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -894,13 +894,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -908,13 +908,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -922,13 +922,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -936,13 +936,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -950,13 +950,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -964,13 +964,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -978,13 +978,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -992,13 +992,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1006,13 +1006,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
       </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1048,13 +1048,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
         <v>50</v>
       </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1062,13 +1062,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
         <v>52</v>
       </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1076,13 +1076,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1093,13 +1093,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1110,13 +1110,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="B28" t="s">
-        <v>57</v>
-      </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1127,13 +1127,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -1144,13 +1144,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
       </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
         <v>60</v>
       </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
         <v>60</v>
       </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
         <v>62</v>
       </c>
-      <c r="B33" t="s">
-        <v>63</v>
-      </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
         <v>62</v>
       </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s">
         <v>64</v>
       </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1240,13 +1240,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" t="s">
         <v>66</v>
       </c>
-      <c r="B36" t="s">
-        <v>67</v>
-      </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1257,13 +1257,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" t="s">
         <v>66</v>
       </c>
-      <c r="B37" t="s">
-        <v>67</v>
-      </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" t="s">
         <v>68</v>
       </c>
-      <c r="B38" t="s">
-        <v>69</v>
-      </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1288,13 +1288,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
         <v>70</v>
       </c>
-      <c r="B39" t="s">
-        <v>71</v>
-      </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1302,13 +1302,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
         <v>72</v>
       </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1330,13 +1330,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" t="s">
         <v>76</v>
       </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1344,13 +1344,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" t="s">
         <v>78</v>
       </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1358,13 +1358,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s">
         <v>80</v>
       </c>
-      <c r="B44" t="s">
-        <v>81</v>
-      </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1372,13 +1372,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s">
         <v>82</v>
       </c>
-      <c r="B45" t="s">
-        <v>83</v>
-      </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1389,13 +1389,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" t="s">
         <v>82</v>
       </c>
-      <c r="B46" t="s">
-        <v>83</v>
-      </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1406,13 +1406,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" t="s">
         <v>84</v>
       </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1423,13 +1423,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" t="s">
         <v>84</v>
       </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1440,13 +1440,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" t="s">
         <v>86</v>
       </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1457,13 +1457,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
         <v>86</v>
       </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1474,13 +1474,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
         <v>88</v>
       </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1491,13 +1491,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
         <v>88</v>
       </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -1508,13 +1508,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
         <v>90</v>
       </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1522,13 +1522,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" t="s">
         <v>92</v>
       </c>
-      <c r="B54" t="s">
-        <v>93</v>
-      </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D54">
         <v>1</v>
